--- a/docs/downloads/09/t9_strategies_marovoay_tous.xlsx
+++ b/docs/downloads/09/t9_strategies_marovoay_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -434,7 +434,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -449,7 +449,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -569,7 +569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -914,7 +914,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1034,7 +1034,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1274,7 +1274,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
